--- a/Arquivos-Escopo/Historia do Usuario 1.xlsx
+++ b/Arquivos-Escopo/Historia do Usuario 1.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20384"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTG-2025\OneDrive - SESISENAISP - Escolas\Área de Trabalho\AgroFlux2026\Arquivos-Escopo\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="17" documentId="11_72C33049B05EED2795AA0C7F82708E77DC0EED3C" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{F6B6D1EC-29DE-4BBD-A9D1-0531F68A8BBB}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
@@ -22,142 +27,124 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
-    <t xml:space="preserve">ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HISTÓRIA DO USUÁRIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REQUISITOS RELACIONADOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HU01</t>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>HISTÓRIA DO USUÁRIO</t>
+  </si>
+  <si>
+    <t>REQUISITOS RELACIONADOS</t>
+  </si>
+  <si>
+    <t>HU01</t>
+  </si>
+  <si>
+    <t>RF03</t>
+  </si>
+  <si>
+    <t>HU02</t>
+  </si>
+  <si>
+    <t>RF06</t>
+  </si>
+  <si>
+    <t>HU03</t>
+  </si>
+  <si>
+    <t>RF08</t>
+  </si>
+  <si>
+    <t>HU04</t>
+  </si>
+  <si>
+    <t>RF09</t>
+  </si>
+  <si>
+    <t>HU05</t>
+  </si>
+  <si>
+    <t>RF10</t>
+  </si>
+  <si>
+    <t>HU06</t>
+  </si>
+  <si>
+    <t>RF04</t>
+  </si>
+  <si>
+    <t>HU07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RF05 </t>
+  </si>
+  <si>
+    <t>HU08</t>
+  </si>
+  <si>
+    <t>RF02</t>
   </si>
   <si>
     <t xml:space="preserve">Como usuário, 
 quero cadastrar produtos 
-Para controlar o estoque da empresa. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HU02</t>
+para controlar o estoque da empresa. </t>
   </si>
   <si>
     <t xml:space="preserve">Como administrador, 
 quero visualizar, listar, atualizar e 
-Deletar dados de funcionários 
+deletar dados de funcionários 
 para manter o controle da equipe. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HU03</t>
   </si>
   <si>
     <t xml:space="preserve">Como usuário, 
 quero sair do sistema através 
-Do botão de logout 
+do botão de logout 
 para garantir a segurança da 
-Minha conta. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HU04</t>
+minha conta. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como usuário, 
+quero editar dados já cadastrados 
+para manter as informações 
+atualizadas. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como gestor, 
+quero visualizar um resumo de vendas, 
+lucros e custos na página inicial 
+para acompanhar o desempenho 
+da empresa. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como funcionário, 
+quero cadastrar clientes no sistema 
+para manter os dados organizados. </t>
   </si>
   <si>
     <t xml:space="preserve">Como usuário, 
 quero acessar uma página de 
 informações gerais 
 para visualizar os dados com 
-Mais detalhes. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HU05</t>
+mais detalhes. </t>
   </si>
   <si>
     <t xml:space="preserve">Como usuário, 
-quero editar dados já cadastrados 
-Para manter as informações 
-Atualizadas. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HU06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como funcionário, 
 quero procurar e visualizar produtos 
-No estoque 
+no estoque 
 para acompanhar a disponibilidade. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HU07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como gestor, 
-quero visualizar um resumo de vendas, 
-lucros e custos na página inicial 
-para acompanhar o desempenho 
-Da empresa. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF05 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">HU08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como funcionário, 
-quero cadastrar clientes no sistema 
-Para manter os dados organizados. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF02</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -201,84 +188,58 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -337,62 +298,78 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -445,23 +422,22 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:D10"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="39.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="36.73"/>
+    <col min="2" max="2" width="11.5546875" style="1"/>
+    <col min="3" max="3" width="39.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="36.77734375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="2:4" ht="15.6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -472,99 +448,98 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="2:4" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="6" t="s">
+    </row>
+    <row r="4" spans="2:4" ht="64.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="61.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="5" t="s">
+    </row>
+    <row r="5" spans="2:4" ht="79.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="C5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
+    <row r="6" spans="2:4" ht="76.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="6" t="s">
+    </row>
+    <row r="7" spans="2:4" ht="61.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="67.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
+      <c r="C7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="5" t="s">
+    </row>
+    <row r="8" spans="2:4" ht="64.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="C8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="s">
+    <row r="9" spans="2:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="B9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="6" t="s">
+    </row>
+    <row r="10" spans="2:4" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4" t="s">
+      <c r="C10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>26</v>
-      </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;CPágina &amp;P</oddFooter>
   </headerFooter>
